--- a/src/main/resources/Pendientes.xlsx
+++ b/src/main/resources/Pendientes.xlsx
@@ -5,11 +5,12 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
+    <sheet name="temas tecnicos" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -21,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="152" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
   <si>
     <t xml:space="preserve">https://www.hellointerview.com/</t>
   </si>
@@ -486,6 +487,117 @@
   </si>
   <si>
     <t xml:space="preserve">allows for...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">just gearing up to...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hang in ther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How’s ....looking there?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i hope so. talk to you soon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...be aware of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">we will mke it...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...made so far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">what time works best for...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">throughtout the day...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">streamline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I’m excited about...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seamless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">downtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">furthermore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tailored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">by now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">since you’re</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regarless of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuando se debe utilizar by despue de un verbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...is preferrred over ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linearly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sequentially</t>
+  </si>
+  <si>
+    <t xml:space="preserve">can be done faster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which at least....</t>
+  </si>
+  <si>
+    <t xml:space="preserve">pedir al chat la explicación de una db con grafos solución a problemas</t>
+  </si>
+  <si>
+    <t xml:space="preserve">solución a problemas de busqueda segun papes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">donde buscar pappes</t>
+  </si>
+  <si>
+    <t xml:space="preserve">explicación tecnica de los grafos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">qie spn perots</t>
+  </si>
+  <si>
+    <t xml:space="preserve">que es un perceptron</t>
+  </si>
+  <si>
+    <t xml:space="preserve">que abreviaciones deberia saber sobre los grafos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">BFS, DFs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">que herramientas puedo utilizar</t>
   </si>
 </sst>
 </file>
@@ -1494,7 +1606,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B22"/>
+  <dimension ref="A1:B57"/>
   <sheetFormatPr defaultColWidth="88.578125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="88.58"/>
@@ -1574,6 +1686,210 @@
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="1" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A27" s="1" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A28" s="1" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A29" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A30" s="1" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A31" s="1" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A32" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A33" s="1" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A34" s="1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A35" s="1" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A37" s="1" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="1" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="1" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A41" s="1" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A42" s="1" t="s">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A43" s="1" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A44" s="1" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A45" s="1" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A46" s="1" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="1" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="1" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="1" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A52" s="1" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A53" s="1" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A55" s="1" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:B17"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="0" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="0" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="0" t="s">
+        <v>182</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="0" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="0" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="0" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="0" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="0" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="0" t="s">
+        <v>188</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Pendientes.xlsx
+++ b/src/main/resources/Pendientes.xlsx
@@ -5,12 +5,13 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="2"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="Sheet2" sheetId="2" state="visible" r:id="rId4"/>
     <sheet name="temas tecnicos" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="revisar" sheetId="4" state="visible" r:id="rId6"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
@@ -22,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
   <si>
     <t xml:space="preserve">https://www.hellointerview.com/</t>
   </si>
@@ -447,13 +448,112 @@
     <t xml:space="preserve">https://articulo.mercadolibre.com.co/MCO-572111822-protector-de-voltaje-breakermatic-nevera-110v-_JM</t>
   </si>
   <si>
+    <t xml:space="preserve">... solves it by verb + ing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...be aware of?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...is preferrred over ...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...made so far</t>
+  </si>
+  <si>
+    <t xml:space="preserve">allows for...</t>
+  </si>
+  <si>
     <t xml:space="preserve">along with...</t>
   </si>
   <si>
+    <t xml:space="preserve">belong to...itselft</t>
+  </si>
+  <si>
+    <t xml:space="preserve">by now</t>
+  </si>
+  <si>
+    <t xml:space="preserve">can be done faster</t>
+  </si>
+  <si>
+    <t xml:space="preserve">como puedo decir debo colgar mi ropa recien lavada</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuando se debe utilizar by despue de un verbo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">downtime</t>
+  </si>
+  <si>
+    <t xml:space="preserve">eager</t>
+  </si>
+  <si>
+    <t xml:space="preserve">furthermore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">futhermore</t>
+  </si>
+  <si>
+    <t xml:space="preserve">hang in ther</t>
+  </si>
+  <si>
+    <t xml:space="preserve">has done</t>
+  </si>
+  <si>
+    <t xml:space="preserve">heavily</t>
+  </si>
+  <si>
+    <t xml:space="preserve">how is</t>
+  </si>
+  <si>
+    <t xml:space="preserve">como es qie se implementa</t>
+  </si>
+  <si>
+    <t xml:space="preserve">How’s ....looking there?</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i hope so. talk to you soon</t>
+  </si>
+  <si>
+    <t xml:space="preserve">I’m excited about...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it solves it by allowing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">just gearing up to...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">just like a class</t>
+  </si>
+  <si>
+    <t xml:space="preserve">kites</t>
+  </si>
+  <si>
+    <t xml:space="preserve">linearly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mainly</t>
+  </si>
+  <si>
     <t xml:space="preserve">moreover</t>
   </si>
   <si>
-    <t xml:space="preserve">futhermore</t>
+    <t xml:space="preserve">pride</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regardless of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">regarless of</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seamless</t>
+  </si>
+  <si>
+    <t xml:space="preserve">sequentially</t>
+  </si>
+  <si>
+    <t xml:space="preserve">since you’re</t>
   </si>
   <si>
     <t xml:space="preserve">so now</t>
@@ -462,117 +562,39 @@
     <t xml:space="preserve">something being inherited from</t>
   </si>
   <si>
-    <t xml:space="preserve">just like a class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regardless of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">how is</t>
-  </si>
-  <si>
-    <t xml:space="preserve">como es qie se implementa</t>
-  </si>
-  <si>
-    <t xml:space="preserve">... solves it by verb + ing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mainly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heavily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">como puedo decir debo colgar mi ropa recien lavada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allows for...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">just gearing up to...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hang in ther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">How’s ....looking there?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i hope so. talk to you soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...be aware of?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has done</t>
+    <t xml:space="preserve">streamline</t>
+  </si>
+  <si>
+    <t xml:space="preserve">tailored</t>
+  </si>
+  <si>
+    <t xml:space="preserve">throughtout the day...</t>
   </si>
   <si>
     <t xml:space="preserve">we will mke it...</t>
   </si>
   <si>
-    <t xml:space="preserve">...made so far</t>
-  </si>
-  <si>
     <t xml:space="preserve">what time works best for...</t>
   </si>
   <si>
-    <t xml:space="preserve">throughtout the day...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">streamline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I’m excited about...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seamless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">downtime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">furthermore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tailored</t>
-  </si>
-  <si>
-    <t xml:space="preserve">by now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">since you’re</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regarless of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuando se debe utilizar by despue de un verbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...is preferrred over ...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">linearly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sequentially</t>
-  </si>
-  <si>
-    <t xml:space="preserve">can be done faster</t>
-  </si>
-  <si>
     <t xml:space="preserve">which at least....</t>
   </si>
   <si>
+    <t xml:space="preserve">whee each....</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...are also known as...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">used heavily...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">which each..is assigned...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">advocatest for</t>
+  </si>
+  <si>
     <t xml:space="preserve">pedir al chat la explicación de una db con grafos solución a problemas</t>
   </si>
   <si>
@@ -598,6 +620,15 @@
   </si>
   <si>
     <t xml:space="preserve">que herramientas puedo utilizar</t>
+  </si>
+  <si>
+    <t xml:space="preserve">como trabaja nlos compiladores segun la teoria de los grafos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">-question</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 mow much</t>
   </si>
 </sst>
 </file>
@@ -693,7 +724,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -714,6 +745,10 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -723,6 +758,23 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF000000"/>
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor rgb="FF000000"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -1606,7 +1658,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B57"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr defaultColWidth="88.578125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="88.58"/>
@@ -1620,212 +1672,247 @@
         <v>137</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="s">
+        <v>139</v>
+      </c>
+    </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>144</v>
+        <v>146</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="s">
+        <v>147</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>145</v>
-      </c>
-      <c r="B12" s="1" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>147</v>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A14" s="1" t="s">
+        <v>150</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="1" t="s">
-        <v>149</v>
+        <v>152</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A17" s="1" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A18" s="1" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A19" s="1" t="s">
+        <v>155</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
+      </c>
+      <c r="B20" s="1" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A21" s="1" t="s">
+        <v>158</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
+      </c>
+    </row>
+    <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="1" t="s">
+        <v>160</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>152</v>
+        <v>161</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>153</v>
+        <v>162</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>154</v>
+        <v>163</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="1" t="s">
-        <v>155</v>
+        <v>164</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="1" t="s">
-        <v>156</v>
+        <v>165</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="1" t="s">
-        <v>157</v>
+        <v>166</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="1" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="1" t="s">
-        <v>159</v>
+        <v>168</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="1" t="s">
-        <v>160</v>
+        <v>169</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="1" t="s">
-        <v>161</v>
+        <v>170</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="1" t="s">
-        <v>162</v>
+        <v>171</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="1" t="s">
-        <v>163</v>
+        <v>172</v>
+      </c>
+    </row>
+    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A36" s="1" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="1" t="s">
-        <v>164</v>
+        <v>174</v>
+      </c>
+    </row>
+    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A38" s="1" t="s">
+        <v>175</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="1" t="s">
-        <v>165</v>
+        <v>176</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="1" t="s">
-        <v>166</v>
+        <v>177</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="1" t="s">
-        <v>167</v>
+        <v>178</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="1" t="s">
-        <v>168</v>
+        <v>179</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="1" t="s">
-        <v>169</v>
+        <v>180</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="1" t="s">
-        <v>170</v>
+        <v>181</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="1" t="s">
-        <v>171</v>
+        <v>182</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="1" t="s">
-        <v>172</v>
+        <v>183</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="1" t="s">
-        <v>175</v>
+        <v>184</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A51" s="1" t="s">
+        <v>185</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="53" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="57" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="1" t="s">
-        <v>179</v>
+        <v>186</v>
       </c>
     </row>
   </sheetData>
@@ -1844,52 +1931,86 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B17"/>
+  <dimension ref="B2:B20"/>
+  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetData>
+    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B2" s="5" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B4" s="5" t="s">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B5" s="5" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B7" s="5" t="s">
+        <v>190</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B8" s="5" t="s">
+        <v>191</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B10" s="5" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B13" s="5" t="s">
+        <v>193</v>
+      </c>
+    </row>
+    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B14" s="5" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B17" s="5" t="s">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B20" s="0" t="s">
+        <v>196</v>
+      </c>
+    </row>
+  </sheetData>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;A</oddHeader>
+    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12Page &amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="B2:B3"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="0" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B5" s="0" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B7" s="0" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B8" s="0" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B10" s="0" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B13" s="0" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B14" s="0" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B17" s="0" t="s">
-        <v>188</v>
+        <v>197</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="B3" s="0" t="s">
+        <v>198</v>
       </c>
     </row>
   </sheetData>

--- a/src/main/resources/Pendientes.xlsx
+++ b/src/main/resources/Pendientes.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="3"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="175">
   <si>
     <t xml:space="preserve">https://www.hellointerview.com/</t>
   </si>
@@ -442,157 +442,79 @@
     <t xml:space="preserve">https://www.amazon.com/Seven-Concurrency-Models-Weeks-Programmers/dp/1937785653/</t>
   </si>
   <si>
-    <t xml:space="preserve">ups</t>
+    <t xml:space="preserve">i tried calling</t>
   </si>
   <si>
     <t xml:space="preserve">https://articulo.mercadolibre.com.co/MCO-572111822-protector-de-voltaje-breakermatic-nevera-110v-_JM</t>
   </si>
   <si>
-    <t xml:space="preserve">... solves it by verb + ing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...be aware of?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...is preferrred over ...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...made so far</t>
-  </si>
-  <si>
-    <t xml:space="preserve">allows for...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">along with...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">belong to...itselft</t>
-  </si>
-  <si>
-    <t xml:space="preserve">by now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">can be done faster</t>
-  </si>
-  <si>
-    <t xml:space="preserve">como puedo decir debo colgar mi ropa recien lavada</t>
-  </si>
-  <si>
-    <t xml:space="preserve">cuando se debe utilizar by despue de un verbo</t>
-  </si>
-  <si>
-    <t xml:space="preserve">downtime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">eager</t>
-  </si>
-  <si>
-    <t xml:space="preserve">furthermore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">futhermore</t>
-  </si>
-  <si>
-    <t xml:space="preserve">hang in ther</t>
-  </si>
-  <si>
-    <t xml:space="preserve">has done</t>
-  </si>
-  <si>
-    <t xml:space="preserve">heavily</t>
-  </si>
-  <si>
-    <t xml:space="preserve">how is</t>
+    <t xml:space="preserve">ahead</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...such as verb+ing and verb+ing</t>
+  </si>
+  <si>
+    <t xml:space="preserve">went smoothly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i reccomend taking...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">...was less.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">fondness</t>
+  </si>
+  <si>
+    <t xml:space="preserve">trade-offs</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boilerplate</t>
+  </si>
+  <si>
+    <t xml:space="preserve">suitable</t>
+  </si>
+  <si>
+    <t xml:space="preserve">underlying</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thresholds</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it mains purpose...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">malformed</t>
+  </si>
+  <si>
+    <t xml:space="preserve">cuando usar o como usar by</t>
+  </si>
+  <si>
+    <t xml:space="preserve">for so-called</t>
+  </si>
+  <si>
+    <t xml:space="preserve">thrive in</t>
+  </si>
+  <si>
+    <t xml:space="preserve">i excel</t>
   </si>
   <si>
     <t xml:space="preserve">como es qie se implementa</t>
   </si>
   <si>
-    <t xml:space="preserve">How’s ....looking there?</t>
-  </si>
-  <si>
-    <t xml:space="preserve">i hope so. talk to you soon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">I’m excited about...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">it solves it by allowing</t>
-  </si>
-  <si>
-    <t xml:space="preserve">just gearing up to...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">just like a class</t>
-  </si>
-  <si>
-    <t xml:space="preserve">kites</t>
-  </si>
-  <si>
-    <t xml:space="preserve">linearly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">mainly</t>
-  </si>
-  <si>
-    <t xml:space="preserve">moreover</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pride</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regardless of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">regarless of</t>
-  </si>
-  <si>
-    <t xml:space="preserve">seamless</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sequentially</t>
-  </si>
-  <si>
-    <t xml:space="preserve">since you’re</t>
-  </si>
-  <si>
-    <t xml:space="preserve">so now</t>
-  </si>
-  <si>
-    <t xml:space="preserve">something being inherited from</t>
-  </si>
-  <si>
-    <t xml:space="preserve">streamline</t>
-  </si>
-  <si>
-    <t xml:space="preserve">tailored</t>
-  </si>
-  <si>
-    <t xml:space="preserve">throughtout the day...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">we will mke it...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">what time works best for...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">which at least....</t>
-  </si>
-  <si>
-    <t xml:space="preserve">whee each....</t>
-  </si>
-  <si>
-    <t xml:space="preserve">...are also known as...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">used heavily...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">which each..is assigned...</t>
-  </si>
-  <si>
-    <t xml:space="preserve">advocatest for</t>
+    <t xml:space="preserve">flawlessly</t>
+  </si>
+  <si>
+    <t xml:space="preserve">nowhere</t>
+  </si>
+  <si>
+    <t xml:space="preserve">just anyplace</t>
+  </si>
+  <si>
+    <t xml:space="preserve">it felt like...</t>
+  </si>
+  <si>
+    <t xml:space="preserve">argue</t>
   </si>
   <si>
     <t xml:space="preserve">pedir al chat la explicación de una db con grafos solución a problemas</t>
@@ -623,6 +545,12 @@
   </si>
   <si>
     <t xml:space="preserve">como trabaja nlos compiladores segun la teoria de los grafos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">T-sql</t>
+  </si>
+  <si>
+    <t xml:space="preserve">KQL</t>
   </si>
   <si>
     <t xml:space="preserve">-question</t>
@@ -758,23 +686,6 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF000000"/>
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <bgColor rgb="FF000000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
 </styleSheet>
 </file>
 
@@ -1658,7 +1569,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:B52"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr defaultColWidth="88.578125" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="1" style="1" width="88.58"/>
@@ -1687,234 +1598,108 @@
         <v>140</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="1" t="s">
-        <v>141</v>
-      </c>
-    </row>
+    <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="6" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="1" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="1" t="s">
-        <v>152</v>
-      </c>
-    </row>
+        <v>150</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="1" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="1" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="1" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="1" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="1" t="s">
-        <v>159</v>
-      </c>
-    </row>
+        <v>156</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
     <row r="23" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="1" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="1" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="1" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="1" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="27" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="1" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="28" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="1" t="s">
-        <v>165</v>
-      </c>
-    </row>
-    <row r="29" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="1" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="1" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="1" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="32" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="1" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="33" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="1" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="34" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="1" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="35" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="1" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="36" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="1" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="37" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="1" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="38" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="39" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="1" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="40" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="1" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="41" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="1" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="42" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="1" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="43" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="1" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="44" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="1" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="45" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="46" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="1" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="47" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="1" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="51" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="1" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="52" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="1" t="s">
-        <v>186</v>
-      </c>
-    </row>
+        <v>160</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="9.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -1931,57 +1716,67 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="B2:B20"/>
+  <dimension ref="B2:B24"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B2" s="5" t="s">
-        <v>187</v>
+        <v>161</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B4" s="5" t="s">
-        <v>188</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B5" s="5" t="s">
-        <v>189</v>
+        <v>163</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B7" s="5" t="s">
-        <v>190</v>
+        <v>164</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B8" s="5" t="s">
-        <v>191</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B10" s="5" t="s">
-        <v>192</v>
+        <v>166</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B13" s="5" t="s">
-        <v>193</v>
+        <v>167</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B14" s="5" t="s">
-        <v>194</v>
+        <v>168</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="B17" s="5" t="s">
-        <v>195</v>
+        <v>169</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B20" s="0" t="s">
-        <v>196</v>
+      <c r="B20" s="5" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="22" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B22" s="0" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="24" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B24" s="0" t="s">
+        <v>172</v>
       </c>
     </row>
   </sheetData>
@@ -2004,13 +1799,13 @@
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="s">
-        <v>197</v>
+      <c r="B2" s="5" t="s">
+        <v>173</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="s">
-        <v>198</v>
+      <c r="B3" s="5" t="s">
+        <v>174</v>
       </c>
     </row>
   </sheetData>
